--- a/CORD_stats.xlsx
+++ b/CORD_stats.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO76"/>
+  <dimension ref="A1:AO77"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="25.1640625" customWidth="1" min="1" max="39"/>
@@ -9334,7 +9334,137 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" ht="15.75" customHeight="1"/>
+    <row r="77" ht="15.75" customHeight="1">
+      <c r="A77" s="21" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Added in 0.1.3</t>
+        </is>
+      </c>
+      <c r="C77" s="22" t="inlineStr">
+        <is>
+          <t>opendata2</t>
+        </is>
+      </c>
+      <c r="D77" s="7" t="inlineStr">
+        <is>
+          <t>lasvegas</t>
+        </is>
+      </c>
+      <c r="E77" s="8" t="n">
+        <v>2026444</v>
+      </c>
+      <c r="F77" s="9" t="n">
+        <v>1668368</v>
+      </c>
+      <c r="G77" s="10" t="n">
+        <v>358076</v>
+      </c>
+      <c r="H77" s="23" t="n">
+        <v>2363611</v>
+      </c>
+      <c r="I77" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" s="23" t="n">
+        <v>1993948</v>
+      </c>
+      <c r="M77" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N77" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O77" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R77" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S77" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T77" s="23" t="n">
+        <v>326525</v>
+      </c>
+      <c r="U77" s="23" t="n">
+        <v>28548</v>
+      </c>
+      <c r="V77" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W77" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X77" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y77" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z77" s="23" t="n">
+        <v>394055</v>
+      </c>
+      <c r="AA77" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB77" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC77" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD77" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE77" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF77" s="23" t="n">
+        <v>350908</v>
+      </c>
+      <c r="AG77" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH77" s="23" t="n">
+        <v>7430</v>
+      </c>
+      <c r="AI77" s="23" t="n">
+        <v>447</v>
+      </c>
+      <c r="AJ77" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK77" s="23" t="n">
+        <v>631846</v>
+      </c>
+      <c r="AL77" s="23" t="n">
+        <v>1394598</v>
+      </c>
+      <c r="AM77" t="n">
+        <v>1654959</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO77" t="n">
+        <v>0</v>
+      </c>
+    </row>
     <row r="78" ht="15.75" customHeight="1"/>
     <row r="79" ht="15.75" customHeight="1"/>
     <row r="80" ht="15.75" customHeight="1"/>

--- a/CORD_stats.xlsx
+++ b/CORD_stats.xlsx
@@ -9340,7 +9340,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Added in 0.1.3</t>
+          <t>Changed in 0.1.4</t>
         </is>
       </c>
       <c r="C77" s="22" t="inlineStr">
@@ -9354,16 +9354,16 @@
         </is>
       </c>
       <c r="E77" s="8" t="n">
-        <v>2026444</v>
+        <v>4052888</v>
       </c>
       <c r="F77" s="9" t="n">
-        <v>1668368</v>
+        <v>3336736</v>
       </c>
       <c r="G77" s="10" t="n">
-        <v>358076</v>
+        <v>716152</v>
       </c>
       <c r="H77" s="23" t="n">
-        <v>2363611</v>
+        <v>4727222</v>
       </c>
       <c r="I77" s="23" t="n">
         <v>0</v>
@@ -9375,7 +9375,7 @@
         <v>0</v>
       </c>
       <c r="L77" s="23" t="n">
-        <v>1993948</v>
+        <v>3987896</v>
       </c>
       <c r="M77" s="23" t="n">
         <v>0</v>
@@ -9399,10 +9399,10 @@
         <v>0</v>
       </c>
       <c r="T77" s="23" t="n">
-        <v>326525</v>
+        <v>653050</v>
       </c>
       <c r="U77" s="23" t="n">
-        <v>28548</v>
+        <v>57096</v>
       </c>
       <c r="V77" s="23" t="n">
         <v>0</v>
@@ -9417,7 +9417,7 @@
         <v>0</v>
       </c>
       <c r="Z77" s="23" t="n">
-        <v>394055</v>
+        <v>788110</v>
       </c>
       <c r="AA77" s="23" t="n">
         <v>0</v>
@@ -9435,28 +9435,28 @@
         <v>0</v>
       </c>
       <c r="AF77" s="23" t="n">
-        <v>350908</v>
+        <v>701816</v>
       </c>
       <c r="AG77" s="23" t="n">
         <v>0</v>
       </c>
       <c r="AH77" s="23" t="n">
-        <v>7430</v>
+        <v>14860</v>
       </c>
       <c r="AI77" s="23" t="n">
-        <v>447</v>
+        <v>894</v>
       </c>
       <c r="AJ77" s="23" t="n">
         <v>0</v>
       </c>
       <c r="AK77" s="23" t="n">
-        <v>631846</v>
+        <v>1263692</v>
       </c>
       <c r="AL77" s="23" t="n">
-        <v>1394598</v>
+        <v>2789196</v>
       </c>
       <c r="AM77" t="n">
-        <v>1654959</v>
+        <v>3309918</v>
       </c>
       <c r="AN77" t="n">
         <v>0</v>

--- a/CORD_stats.xlsx
+++ b/CORD_stats.xlsx
@@ -8973,7 +8973,12 @@
     </row>
     <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="5" t="n">
-        <v>45724</v>
+        <v>46325</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Added in 0.1.5</t>
+        </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>

--- a/CORD_stats.xlsx
+++ b/CORD_stats.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO77"/>
+  <dimension ref="A1:AO78"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="25.1640625" customWidth="1" min="1" max="39"/>
@@ -9470,7 +9470,137 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" ht="15.75" customHeight="1"/>
+    <row r="78" ht="15.75" customHeight="1">
+      <c r="A78" s="21" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Added in 0.1.6</t>
+        </is>
+      </c>
+      <c r="C78" s="22" t="inlineStr">
+        <is>
+          <t>opendata3</t>
+        </is>
+      </c>
+      <c r="D78" s="7" t="inlineStr">
+        <is>
+          <t>lasvegas</t>
+        </is>
+      </c>
+      <c r="E78" s="8" t="n">
+        <v>2026444</v>
+      </c>
+      <c r="F78" s="9" t="n">
+        <v>1668368</v>
+      </c>
+      <c r="G78" s="10" t="n">
+        <v>358076</v>
+      </c>
+      <c r="H78" s="23" t="n">
+        <v>2363611</v>
+      </c>
+      <c r="I78" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" s="23" t="n">
+        <v>1993948</v>
+      </c>
+      <c r="M78" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N78" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q78" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R78" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T78" s="23" t="n">
+        <v>326525</v>
+      </c>
+      <c r="U78" s="23" t="n">
+        <v>28548</v>
+      </c>
+      <c r="V78" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W78" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X78" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y78" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z78" s="23" t="n">
+        <v>394055</v>
+      </c>
+      <c r="AA78" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB78" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC78" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD78" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE78" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF78" s="23" t="n">
+        <v>350908</v>
+      </c>
+      <c r="AG78" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH78" s="23" t="n">
+        <v>7430</v>
+      </c>
+      <c r="AI78" s="23" t="n">
+        <v>447</v>
+      </c>
+      <c r="AJ78" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK78" s="23" t="n">
+        <v>631846</v>
+      </c>
+      <c r="AL78" s="23" t="n">
+        <v>1394598</v>
+      </c>
+      <c r="AM78" t="n">
+        <v>1654959</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO78" t="n">
+        <v>0</v>
+      </c>
+    </row>
     <row r="79" ht="15.75" customHeight="1"/>
     <row r="80" ht="15.75" customHeight="1"/>
     <row r="81" ht="15.75" customHeight="1"/>

--- a/CORD_stats.xlsx
+++ b/CORD_stats.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO78"/>
+  <dimension ref="A1:AO79"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="25.1640625" customWidth="1" min="1" max="39"/>
@@ -9601,7 +9601,137 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" ht="15.75" customHeight="1"/>
+    <row r="79" ht="15.75" customHeight="1">
+      <c r="A79" s="21" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Added in 0.1.7</t>
+        </is>
+      </c>
+      <c r="C79" s="22" t="inlineStr">
+        <is>
+          <t>opendata4</t>
+        </is>
+      </c>
+      <c r="D79" s="7" t="inlineStr">
+        <is>
+          <t>lasvegas</t>
+        </is>
+      </c>
+      <c r="E79" s="8" t="n">
+        <v>4052888</v>
+      </c>
+      <c r="F79" s="9" t="n">
+        <v>3336736</v>
+      </c>
+      <c r="G79" s="10" t="n">
+        <v>716152</v>
+      </c>
+      <c r="H79" s="23" t="n">
+        <v>4727222</v>
+      </c>
+      <c r="I79" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" s="23" t="n">
+        <v>3987896</v>
+      </c>
+      <c r="M79" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N79" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O79" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q79" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R79" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S79" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T79" s="23" t="n">
+        <v>653050</v>
+      </c>
+      <c r="U79" s="23" t="n">
+        <v>57096</v>
+      </c>
+      <c r="V79" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W79" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X79" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y79" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z79" s="23" t="n">
+        <v>788110</v>
+      </c>
+      <c r="AA79" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB79" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC79" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD79" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE79" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF79" s="23" t="n">
+        <v>701816</v>
+      </c>
+      <c r="AG79" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH79" s="23" t="n">
+        <v>14860</v>
+      </c>
+      <c r="AI79" s="23" t="n">
+        <v>894</v>
+      </c>
+      <c r="AJ79" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK79" s="23" t="n">
+        <v>1263692</v>
+      </c>
+      <c r="AL79" s="23" t="n">
+        <v>2789196</v>
+      </c>
+      <c r="AM79" t="n">
+        <v>3309918</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO79" t="n">
+        <v>0</v>
+      </c>
+    </row>
     <row r="80" ht="15.75" customHeight="1"/>
     <row r="81" ht="15.75" customHeight="1"/>
     <row r="82" ht="15.75" customHeight="1"/>

--- a/CORD_stats.xlsx
+++ b/CORD_stats.xlsx
@@ -666,11 +666,11 @@
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="5" t="n">
-        <v>46228</v>
+        <v>46325</v>
       </c>
       <c r="B2" s="24" t="inlineStr">
         <is>
-          <t>Added website_risk_propensity (WRP score) and organization_type payload fields from vendor file Senzing_DBI_WRP_MARK_07142026.csv; resolution features unchanged.</t>
+          <t>Added in 0.1.8</t>
         </is>
       </c>
       <c r="C2" s="6" t="inlineStr">
@@ -683,20 +683,14 @@
           <t>lasvegas</t>
         </is>
       </c>
-      <c r="E2" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28,040 </t>
-        </is>
-      </c>
-      <c r="F2" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28,040 </t>
-        </is>
-      </c>
-      <c r="G2" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0 </t>
-        </is>
+      <c r="E2" s="12" t="n">
+        <v>28040</v>
+      </c>
+      <c r="F2" s="13" t="n">
+        <v>28040</v>
+      </c>
+      <c r="G2" s="14" t="n">
+        <v>0</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>28036</v>
